--- a/saida/taxa_servico_2026-10-01_a_2026-10-18.xlsx
+++ b/saida/taxa_servico_2026-10-01_a_2026-10-18.xlsx
@@ -12160,22 +12160,10 @@
           <t>qui</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>MARIANA CHAVES</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>ADM ISAIAS 01</t>
-        </is>
-      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
+      <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
@@ -12236,22 +12224,10 @@
           <t>qui</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>MARIANA CHAVES</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>ADM ISAIAS 01</t>
-        </is>
-      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
+      <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
@@ -12312,22 +12288,10 @@
           <t>qui</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>MARIANA CHAVES</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>ADM ISAIAS 01</t>
-        </is>
-      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
+      <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
@@ -12388,22 +12352,10 @@
           <t>qui</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>MARIANA CHAVES</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>ADM ISAIAS 01</t>
-        </is>
-      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
+      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
@@ -12464,22 +12416,10 @@
           <t>qui</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>MARIANA CHAVES</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>ADM ISAIAS 01</t>
-        </is>
-      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
+      <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
@@ -12540,22 +12480,10 @@
           <t>sex</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>MARIANA CHAVES</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>ADM ISAIAS 01</t>
-        </is>
-      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
+      <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
@@ -12616,22 +12544,10 @@
           <t>sex</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>MARIANA CHAVES</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>ADM ISAIAS 01</t>
-        </is>
-      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
+      <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
@@ -12692,22 +12608,10 @@
           <t>sex</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>MARIANA CHAVES</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>ADM ISAIAS 01</t>
-        </is>
-      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
+      <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
     </row>
     <row r="81">
@@ -12768,22 +12672,10 @@
           <t>sex</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>MARIANA CHAVES</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>ADM ISAIAS 01</t>
-        </is>
-      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
+      <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
@@ -12844,22 +12736,10 @@
           <t>sex</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>MARIANA CHAVES</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>ADM ISAIAS 01</t>
-        </is>
-      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
+      <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
     </row>
     <row r="83">
@@ -12920,22 +12800,10 @@
           <t>sex</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>MARIANA CHAVES</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>ADM ISAIAS 01</t>
-        </is>
-      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>não</t>
-        </is>
-      </c>
+      <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
     </row>
   </sheetData>
@@ -12949,7 +12817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -12990,26 +12858,13 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MARIANA CHAVES</t>
+          <t>LUCAS DE MUSSI PALMA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>216.1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>LUCAS DE MUSSI PALMA</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="n">
         <v>22.25</v>
       </c>
     </row>

--- a/saida/taxa_servico_2026-10-01_a_2026-10-18.xlsx
+++ b/saida/taxa_servico_2026-10-01_a_2026-10-18.xlsx
@@ -12096,10 +12096,26 @@
           <t>qua</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>BRUNO DA SILVA INACIO</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DANIEL BACELAR XAVIER </t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
@@ -12160,10 +12176,26 @@
           <t>qui</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>BRUNO DA SILVA INACIO</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>DAVID FERNANDES DA CRUZ</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
@@ -12224,10 +12256,26 @@
           <t>qui</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>BRUNO DA SILVA INACIO</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
@@ -12288,10 +12336,26 @@
           <t>qui</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>BRUNO DA SILVA INACIO</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>DAVID FERNANDES DA CRUZ</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
@@ -12352,10 +12416,26 @@
           <t>qui</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>BRUNO DA SILVA INACIO</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>DAVID FERNANDES DA CRUZ</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
@@ -12416,10 +12496,26 @@
           <t>qui</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>BRUNO DA SILVA INACIO</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>MATEUS AUGUSTO NASCIMENTO COSTA</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
@@ -12480,10 +12576,26 @@
           <t>sex</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>BRUNO DA SILVA INACIO</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>KEROLAINY LAWANY RIO BRANCO</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
@@ -12544,10 +12656,26 @@
           <t>sex</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>BRUNO DA SILVA INACIO</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
@@ -12608,10 +12736,26 @@
           <t>sex</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>BRUNO DA SILVA INACIO</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>CAIO VINICIUS DOS SANTOS SILVA</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="R80" t="inlineStr"/>
     </row>
     <row r="81">
@@ -12672,10 +12816,26 @@
           <t>sex</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>BRUNO DA SILVA INACIO</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
@@ -12736,10 +12896,26 @@
           <t>sex</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>BRUNO DA SILVA INACIO</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DAIANA APARECIDA DOS SANTOS SILVA ALVES </t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="R82" t="inlineStr"/>
     </row>
     <row r="83">
@@ -12800,10 +12976,26 @@
           <t>sex</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>BRUNO DA SILVA INACIO</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>DAVID FERNANDES DA CRUZ</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="R83" t="inlineStr"/>
     </row>
   </sheetData>
@@ -12849,10 +13041,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C2" t="n">
-        <v>1136.1</v>
+        <v>1371.2</v>
       </c>
     </row>
     <row r="3">

--- a/saida/taxa_servico_2026-10-01_a_2026-10-18.xlsx
+++ b/saida/taxa_servico_2026-10-01_a_2026-10-18.xlsx
@@ -498,10 +498,10 @@
         <v>20</v>
       </c>
       <c r="G2" t="n">
-        <v>204138.81</v>
+        <v>206449.07</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0068</v>
+        <v>0.0067</v>
       </c>
     </row>
     <row r="3">
@@ -526,7 +526,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>73977.81</v>
+        <v>74437.94</v>
       </c>
       <c r="H3" t="n">
         <v>0.0017</v>
@@ -554,7 +554,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>189022.09</v>
+        <v>189121.29</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
